--- a/data/import.xlsx
+++ b/data/import.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plaisancem\Documents\Dev\cfpicks\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4BD09A6-E0F4-4D27-B214-CA736EEC0297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1981D4AF-546F-49BD-A1F6-7419ACD53E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>date</t>
   </si>
@@ -44,43 +44,70 @@
     <t>home</t>
   </si>
   <si>
-    <t>Georgia</t>
-  </si>
-  <si>
-    <t>Alabama</t>
-  </si>
-  <si>
-    <t>Ohio St</t>
-  </si>
-  <si>
-    <t>Tulane</t>
-  </si>
-  <si>
-    <t>Texas Tech</t>
-  </si>
-  <si>
-    <t>Indiana</t>
-  </si>
-  <si>
-    <t>Oklahoma</t>
-  </si>
-  <si>
     <t>Miami</t>
   </si>
   <si>
-    <t>Texas A&amp;M</t>
-  </si>
-  <si>
     <t>Ole Miss</t>
   </si>
   <si>
-    <t>JMU</t>
-  </si>
-  <si>
-    <t>Oregon</t>
-  </si>
-  <si>
-    <t>TBD</t>
+    <t>Colorado</t>
+  </si>
+  <si>
+    <t>Georgia Tech</t>
+  </si>
+  <si>
+    <t>Stanford</t>
+  </si>
+  <si>
+    <t>Oregon St</t>
+  </si>
+  <si>
+    <t>Houston</t>
+  </si>
+  <si>
+    <t>Texas St</t>
+  </si>
+  <si>
+    <t>Texas</t>
+  </si>
+  <si>
+    <t>Baylor</t>
+  </si>
+  <si>
+    <t>Auburn</t>
+  </si>
+  <si>
+    <t>Clemson</t>
+  </si>
+  <si>
+    <t>LSU</t>
+  </si>
+  <si>
+    <t>UNLV</t>
+  </si>
+  <si>
+    <t>Hawaii</t>
+  </si>
+  <si>
+    <t>UCLA</t>
+  </si>
+  <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>Louisville</t>
+  </si>
+  <si>
+    <t>Wisconsin</t>
+  </si>
+  <si>
+    <t>Notre Dame</t>
+  </si>
+  <si>
+    <t>SMU</t>
+  </si>
+  <si>
+    <t>Florida St</t>
   </si>
 </sst>
 </file>
@@ -440,7 +467,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="18.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.7109375" style="2" bestFit="1" customWidth="1"/>
@@ -459,40 +486,40 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>46011.770833333336</v>
+        <v>46268.791666666664</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>46010.791666666664</v>
+        <v>46269.833333333336</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>46011.604166666664</v>
+        <v>46270.458333333336</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>46011.458333333336</v>
+        <v>46270.604166666664</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
@@ -503,79 +530,79 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>46023.458333333336</v>
+        <v>46270.604166666664</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>46023.625</v>
+        <v>46270.770833333336</v>
       </c>
       <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
         <v>15</v>
-      </c>
-      <c r="C7" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>46023.791666666664</v>
+        <v>46270.875</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>46022.791666666664</v>
+        <v>46270.895833333336</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>46031.770833333336</v>
+        <v>46271.770833333336</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>46030.770833333336</v>
+        <v>46271.770833333336</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>46041.770833333336</v>
+        <v>46272.770833333336</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -600,10 +627,7 @@
       <c r="A19"/>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
+      <c r="A20" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/import.xlsx
+++ b/data/import.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plaisancem\Documents\Dev\cfpicks\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1981D4AF-546F-49BD-A1F6-7419ACD53E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E146E8D6-39CE-4446-8293-022CDE47D3B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -44,70 +44,70 @@
     <t>home</t>
   </si>
   <si>
-    <t>Miami</t>
-  </si>
-  <si>
-    <t>Ole Miss</t>
-  </si>
-  <si>
-    <t>Colorado</t>
-  </si>
-  <si>
     <t>Georgia Tech</t>
   </si>
   <si>
-    <t>Stanford</t>
-  </si>
-  <si>
-    <t>Oregon St</t>
-  </si>
-  <si>
-    <t>Houston</t>
-  </si>
-  <si>
-    <t>Texas St</t>
-  </si>
-  <si>
     <t>Texas</t>
   </si>
   <si>
-    <t>Baylor</t>
-  </si>
-  <si>
-    <t>Auburn</t>
-  </si>
-  <si>
-    <t>Clemson</t>
-  </si>
-  <si>
-    <t>LSU</t>
-  </si>
-  <si>
-    <t>UNLV</t>
-  </si>
-  <si>
-    <t>Hawaii</t>
-  </si>
-  <si>
-    <t>UCLA</t>
-  </si>
-  <si>
-    <t>California</t>
-  </si>
-  <si>
-    <t>Louisville</t>
-  </si>
-  <si>
-    <t>Wisconsin</t>
-  </si>
-  <si>
-    <t>Notre Dame</t>
-  </si>
-  <si>
-    <t>SMU</t>
-  </si>
-  <si>
-    <t>Florida St</t>
+    <t>Missouri</t>
+  </si>
+  <si>
+    <t>Kansas</t>
+  </si>
+  <si>
+    <t>Oregon</t>
+  </si>
+  <si>
+    <t>Oklahoma St</t>
+  </si>
+  <si>
+    <t>ASU</t>
+  </si>
+  <si>
+    <t>Texas A&amp;M</t>
+  </si>
+  <si>
+    <t>OU</t>
+  </si>
+  <si>
+    <t>Michigan</t>
+  </si>
+  <si>
+    <t>Alabama</t>
+  </si>
+  <si>
+    <t>Kentucky</t>
+  </si>
+  <si>
+    <t>Mississippi St</t>
+  </si>
+  <si>
+    <t>Minnesota</t>
+  </si>
+  <si>
+    <t>Tennesse</t>
+  </si>
+  <si>
+    <t>Ohio St</t>
+  </si>
+  <si>
+    <t>Arkansas</t>
+  </si>
+  <si>
+    <t>Utah</t>
+  </si>
+  <si>
+    <t>Arizona</t>
+  </si>
+  <si>
+    <t>BYU</t>
+  </si>
+  <si>
+    <t>Memphis</t>
+  </si>
+  <si>
+    <t>Boise St</t>
   </si>
 </sst>
 </file>
@@ -467,7 +467,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultColWidth="18.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.7109375" style="2" bestFit="1" customWidth="1"/>
@@ -486,7 +486,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>46268.791666666664</v>
+        <v>46276.791666666664</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -497,119 +497,119 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>46269.833333333336</v>
+        <v>46277.458333333336</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>46270.458333333336</v>
+        <v>46277.458333333336</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>46270.604166666664</v>
+        <v>46277.458333333336</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>46270.604166666664</v>
+        <v>46277.604166666664</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>46270.770833333336</v>
+        <v>46277.604166666664</v>
       </c>
       <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
         <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>46270.875</v>
+        <v>46277.604166666664</v>
       </c>
       <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
         <v>16</v>
-      </c>
-      <c r="C8" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>46270.895833333336</v>
+        <v>46277.708333333336</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>46271.770833333336</v>
+        <v>46277.75</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>46271.770833333336</v>
+        <v>46277.770833333336</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>46272.770833333336</v>
+        <v>46277.885416666664</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13"/>
+      <c r="A13" s="1"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14"/>
+      <c r="A14" s="1"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15"/>
@@ -627,7 +627,13 @@
       <c r="A19"/>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
+      <c r="A20"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/import.xlsx
+++ b/data/import.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plaisancem\Documents\Dev\cfpicks\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E146E8D6-39CE-4446-8293-022CDE47D3B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F60E20-C879-4BA7-952A-B5CD8E8BC91D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>date</t>
   </si>
@@ -44,70 +44,64 @@
     <t>home</t>
   </si>
   <si>
-    <t>Georgia Tech</t>
-  </si>
-  <si>
-    <t>Texas</t>
-  </si>
-  <si>
-    <t>Missouri</t>
-  </si>
-  <si>
     <t>Kansas</t>
   </si>
   <si>
-    <t>Oregon</t>
-  </si>
-  <si>
-    <t>Oklahoma St</t>
-  </si>
-  <si>
     <t>ASU</t>
   </si>
   <si>
     <t>Texas A&amp;M</t>
   </si>
   <si>
-    <t>OU</t>
-  </si>
-  <si>
-    <t>Michigan</t>
-  </si>
-  <si>
-    <t>Alabama</t>
-  </si>
-  <si>
     <t>Kentucky</t>
   </si>
   <si>
     <t>Mississippi St</t>
   </si>
   <si>
-    <t>Minnesota</t>
-  </si>
-  <si>
-    <t>Tennesse</t>
-  </si>
-  <si>
-    <t>Ohio St</t>
-  </si>
-  <si>
-    <t>Arkansas</t>
-  </si>
-  <si>
-    <t>Utah</t>
-  </si>
-  <si>
-    <t>Arizona</t>
-  </si>
-  <si>
-    <t>BYU</t>
-  </si>
-  <si>
-    <t>Memphis</t>
-  </si>
-  <si>
-    <t>Boise St</t>
+    <t>Houston</t>
+  </si>
+  <si>
+    <t>Texas Tech</t>
+  </si>
+  <si>
+    <t>North Carolina</t>
+  </si>
+  <si>
+    <t>Clemson</t>
+  </si>
+  <si>
+    <t>SMU</t>
+  </si>
+  <si>
+    <t>Louisville</t>
+  </si>
+  <si>
+    <t>South Carolina</t>
+  </si>
+  <si>
+    <t>Florida</t>
+  </si>
+  <si>
+    <t>Auburn</t>
+  </si>
+  <si>
+    <t>LSU</t>
+  </si>
+  <si>
+    <t>Ole Miss</t>
+  </si>
+  <si>
+    <t>Colorado</t>
+  </si>
+  <si>
+    <t>Northwestern</t>
+  </si>
+  <si>
+    <t>NC State</t>
+  </si>
+  <si>
+    <t>Vanderbilt</t>
   </si>
 </sst>
 </file>
@@ -486,124 +480,116 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>46276.791666666664</v>
+        <v>46283.791666666664</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>46277.458333333336</v>
+        <v>46284.458333333336</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>46277.458333333336</v>
+        <v>46284.458333333336</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>46277.458333333336</v>
+        <v>46284.489583333336</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>46277.604166666664</v>
+        <v>46284.604166666664</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>46277.604166666664</v>
+        <v>46284.604166666664</v>
       </c>
       <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
         <v>13</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>46277.604166666664</v>
+        <v>46284.635416666664</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>46277.708333333336</v>
+        <v>46284.75</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>46277.75</v>
+        <v>46284.770833333336</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>46277.770833333336</v>
+        <v>46284.770833333336</v>
       </c>
       <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
         <v>18</v>
       </c>
-      <c r="C11" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>46277.885416666664</v>
-      </c>
-      <c r="B12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" t="s">
-        <v>20</v>
-      </c>
+      <c r="A12" s="1"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>

--- a/data/import.xlsx
+++ b/data/import.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plaisancem\Documents\Dev\cfpicks\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F60E20-C879-4BA7-952A-B5CD8E8BC91D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD88E764-EBCC-4ED2-9DB8-A05E1BE3FB09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>date</t>
   </si>
@@ -44,39 +44,15 @@
     <t>home</t>
   </si>
   <si>
-    <t>Kansas</t>
-  </si>
-  <si>
-    <t>ASU</t>
-  </si>
-  <si>
     <t>Texas A&amp;M</t>
   </si>
   <si>
-    <t>Kentucky</t>
-  </si>
-  <si>
     <t>Mississippi St</t>
   </si>
   <si>
-    <t>Houston</t>
-  </si>
-  <si>
-    <t>Texas Tech</t>
-  </si>
-  <si>
-    <t>North Carolina</t>
-  </si>
-  <si>
     <t>Clemson</t>
   </si>
   <si>
-    <t>SMU</t>
-  </si>
-  <si>
-    <t>Louisville</t>
-  </si>
-  <si>
     <t>South Carolina</t>
   </si>
   <si>
@@ -95,13 +71,49 @@
     <t>Colorado</t>
   </si>
   <si>
-    <t>Northwestern</t>
-  </si>
-  <si>
-    <t>NC State</t>
-  </si>
-  <si>
     <t>Vanderbilt</t>
+  </si>
+  <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>Texas</t>
+  </si>
+  <si>
+    <t>Tennessee</t>
+  </si>
+  <si>
+    <t>Baylor</t>
+  </si>
+  <si>
+    <t>Georgia</t>
+  </si>
+  <si>
+    <t>OU</t>
+  </si>
+  <si>
+    <t>Iowa</t>
+  </si>
+  <si>
+    <t>Michigan</t>
+  </si>
+  <si>
+    <t>Alabama</t>
+  </si>
+  <si>
+    <t>Oklahoma St</t>
+  </si>
+  <si>
+    <t>West Virginia</t>
+  </si>
+  <si>
+    <t>Oregon</t>
+  </si>
+  <si>
+    <t>USC</t>
+  </si>
+  <si>
+    <t>Missouri</t>
   </si>
 </sst>
 </file>
@@ -461,7 +473,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultColWidth="18.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.7109375" style="2" bestFit="1" customWidth="1"/>
@@ -480,125 +492,141 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>46283.791666666664</v>
+        <v>46290.895833333336</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>46284.458333333336</v>
+        <v>46291.458333333336</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>46284.458333333336</v>
+        <v>46291.458333333336</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>46284.489583333336</v>
+        <v>46291.604166666664</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>46284.604166666664</v>
+        <v>46291.604166666664</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>46284.604166666664</v>
+        <v>46291.604166666664</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>46284.635416666664</v>
+        <v>46291.635416666664</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>46284.75</v>
+        <v>46291.75</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>46284.770833333336</v>
+        <v>46291.75</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>46284.770833333336</v>
+        <v>46291.770833333336</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
+      <c r="A12" s="1">
+        <v>46291.770833333336</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
+      <c r="A13" s="1">
+        <v>46291.78125</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15"/>
+      <c r="A15" s="1"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16"/>
@@ -619,7 +647,10 @@
       <c r="A21"/>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
+      <c r="A22"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/import.xlsx
+++ b/data/import.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plaisancem\Documents\Dev\cfpicks\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD88E764-EBCC-4ED2-9DB8-A05E1BE3FB09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{225E619D-6D98-4F6E-8E4C-9E8407B377FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>date</t>
   </si>
@@ -62,58 +62,52 @@
     <t>Auburn</t>
   </si>
   <si>
-    <t>LSU</t>
-  </si>
-  <si>
-    <t>Ole Miss</t>
-  </si>
-  <si>
-    <t>Colorado</t>
-  </si>
-  <si>
-    <t>Vanderbilt</t>
-  </si>
-  <si>
-    <t>California</t>
-  </si>
-  <si>
-    <t>Texas</t>
-  </si>
-  <si>
     <t>Tennessee</t>
   </si>
   <si>
     <t>Baylor</t>
   </si>
   <si>
-    <t>Georgia</t>
-  </si>
-  <si>
-    <t>OU</t>
-  </si>
-  <si>
-    <t>Iowa</t>
-  </si>
-  <si>
     <t>Michigan</t>
   </si>
   <si>
     <t>Alabama</t>
   </si>
   <si>
-    <t>Oklahoma St</t>
-  </si>
-  <si>
-    <t>West Virginia</t>
-  </si>
-  <si>
-    <t>Oregon</t>
-  </si>
-  <si>
-    <t>USC</t>
-  </si>
-  <si>
     <t>Missouri</t>
+  </si>
+  <si>
+    <t>Penn St</t>
+  </si>
+  <si>
+    <t>Northwestern</t>
+  </si>
+  <si>
+    <t>Notre Dame</t>
+  </si>
+  <si>
+    <t>UNC</t>
+  </si>
+  <si>
+    <t>Minnesota</t>
+  </si>
+  <si>
+    <t>Kentucky</t>
+  </si>
+  <si>
+    <t>BYU</t>
+  </si>
+  <si>
+    <t>TCU</t>
+  </si>
+  <si>
+    <t>Arkansas</t>
+  </si>
+  <si>
+    <t>Miami</t>
+  </si>
+  <si>
+    <t>ASU</t>
   </si>
 </sst>
 </file>
@@ -473,7 +467,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultColWidth="18.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.7109375" style="2" bestFit="1" customWidth="1"/>
@@ -492,87 +486,87 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>46290.895833333336</v>
+        <v>46293.791666666664</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>46291.458333333336</v>
+        <v>46298.458333333336</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>46291.458333333336</v>
+        <v>46298.458333333336</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>46291.604166666664</v>
+        <v>46298.458333333336</v>
       </c>
       <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
         <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>46291.604166666664</v>
+        <v>46298.604166666664</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>46291.604166666664</v>
+        <v>46298.604166666664</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>46291.635416666664</v>
+        <v>46298.635416666664</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>46291.75</v>
+        <v>46298.75</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
         <v>21</v>
@@ -580,47 +574,39 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>46291.75</v>
+        <v>46298.75</v>
       </c>
       <c r="B10" t="s">
         <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>46291.770833333336</v>
+        <v>46298.770833333336</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>46291.770833333336</v>
+        <v>46298.895833333336</v>
       </c>
       <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
         <v>24</v>
       </c>
-      <c r="C12" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>46291.78125</v>
-      </c>
-      <c r="B13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" t="s">
-        <v>4</v>
-      </c>
+      <c r="A13" s="1"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
@@ -629,7 +615,7 @@
       <c r="A15" s="1"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16"/>
+      <c r="A16" s="1"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17"/>
@@ -650,7 +636,10 @@
       <c r="A22"/>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
+      <c r="A23"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/import.xlsx
+++ b/data/import.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plaisancem\Documents\Dev\cfpicks\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{225E619D-6D98-4F6E-8E4C-9E8407B377FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6866C66-CAA7-4EC4-8366-6CAFC9EB33D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1500" yWindow="870" windowWidth="25410" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>date</t>
   </si>
@@ -47,30 +47,12 @@
     <t>Texas A&amp;M</t>
   </si>
   <si>
-    <t>Mississippi St</t>
-  </si>
-  <si>
-    <t>Clemson</t>
-  </si>
-  <si>
     <t>South Carolina</t>
   </si>
   <si>
     <t>Florida</t>
   </si>
   <si>
-    <t>Auburn</t>
-  </si>
-  <si>
-    <t>Tennessee</t>
-  </si>
-  <si>
-    <t>Baylor</t>
-  </si>
-  <si>
-    <t>Michigan</t>
-  </si>
-  <si>
     <t>Alabama</t>
   </si>
   <si>
@@ -80,34 +62,46 @@
     <t>Penn St</t>
   </si>
   <si>
-    <t>Northwestern</t>
-  </si>
-  <si>
-    <t>Notre Dame</t>
-  </si>
-  <si>
-    <t>UNC</t>
-  </si>
-  <si>
-    <t>Minnesota</t>
-  </si>
-  <si>
     <t>Kentucky</t>
   </si>
   <si>
-    <t>BYU</t>
-  </si>
-  <si>
-    <t>TCU</t>
-  </si>
-  <si>
-    <t>Arkansas</t>
-  </si>
-  <si>
-    <t>Miami</t>
-  </si>
-  <si>
-    <t>ASU</t>
+    <t>Florida St</t>
+  </si>
+  <si>
+    <t>Louisville</t>
+  </si>
+  <si>
+    <t>Indiana</t>
+  </si>
+  <si>
+    <t>Nebraska</t>
+  </si>
+  <si>
+    <t>Texas</t>
+  </si>
+  <si>
+    <t>OU</t>
+  </si>
+  <si>
+    <t>LSU</t>
+  </si>
+  <si>
+    <t>Georgia</t>
+  </si>
+  <si>
+    <t>UCLA</t>
+  </si>
+  <si>
+    <t>Oregon</t>
+  </si>
+  <si>
+    <t>Houston</t>
+  </si>
+  <si>
+    <t>Kansas St</t>
+  </si>
+  <si>
+    <t>USC</t>
   </si>
 </sst>
 </file>
@@ -467,7 +461,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="18.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.7109375" style="2" bestFit="1" customWidth="1"/>
@@ -486,136 +480,128 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>46293.791666666664</v>
+        <v>46304.75</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>46298.458333333336</v>
+        <v>46305.458333333336</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>46298.458333333336</v>
+        <v>46305.458333333336</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>46298.458333333336</v>
+        <v>46305.489583333336</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>46298.604166666664</v>
+        <v>46305.604166666664</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>46298.604166666664</v>
+        <v>46305.604166666664</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>46298.635416666664</v>
+        <v>46305.604166666664</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>46298.75</v>
+        <v>46305.75</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>46298.75</v>
+        <v>46305.770833333336</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>46298.770833333336</v>
+        <v>46305.770833333336</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>46298.895833333336</v>
-      </c>
-      <c r="B12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" t="s">
-        <v>24</v>
-      </c>
+      <c r="A12" s="1"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
+      <c r="A13"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
+      <c r="A14"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
+      <c r="A15"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
+      <c r="A16"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17"/>
@@ -627,19 +613,7 @@
       <c r="A19"/>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22"/>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23"/>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
+      <c r="A20" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
